--- a/assets/constructions/examples/ctd_arbm_colletchuck.xlsx
+++ b/assets/constructions/examples/ctd_arbm_colletchuck.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,11 +584,31 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MTB3-ER32</t>
+          <t>SK50-ER16-70</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -605,7 +625,7 @@
         <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -613,41 +633,41 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="S2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
-        <v>20</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>15000</v>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>MKG_H:3</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>0.65</v>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
@@ -658,56 +678,56 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>ER32</t>
-        </is>
-      </c>
+          <t>ER16</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HSK100A-GSK16-105P</t>
+          <t>SK30-ER20-70</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Высокоточные цанговые патроны HSK-A-GSK для высокоскоростной обработки</t>
-        </is>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H3" t="n">
-        <v>40.5</v>
+        <v>34</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>100</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DER_ER-16</t>
+          <t>LIK_ER-16</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -725,37 +745,41 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>DIN_69871:SK30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+          <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>DER_DSK_COLLET:16</t>
-        </is>
-      </c>
+          <t>ER20</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK30-ER20-100</t>
+          <t>HSK63A-ER20-100</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -766,27 +790,23 @@
       <c r="F4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>50</v>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LIK_ER-20</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>LIKON</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="S4" t="n">
         <v>0.5</v>
@@ -795,27 +815,33 @@
         <v>13</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>15000</v>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DIN_69871:SK30</t>
+          <t>ISO_12164_1_2013:HSK63A</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2021/YG1_TOOLING</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -823,159 +849,201 @@
           <t>ER20</t>
         </is>
       </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CBT50-ER25-100</t>
+          <t>HSK100A-GSK16-105P</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YG1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Высокоточные цанговые патроны HSK-A-GSK для высокоскоростной обработки</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
-        <v>42</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="H5" t="n">
+        <v>40.5</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>65</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>DER_ER-16</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
       <c r="R5" t="n">
-        <v>25</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
         <v>16</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BBT50</t>
+          <t>ISO_12164_1_2013:HSK100A</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2021/YG1_TOOLING</t>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>ER25</t>
-        </is>
-      </c>
+          <t>DER_DSK_COLLET:16</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT50AD/B-ER32-165</t>
+          <t>BT50-GSK20-150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YG1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Высокоточные цанговые патроны BT-GSK для высокоскоростной обработки</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>48.5</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>65</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DER_ER-20</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
       <c r="R6" t="n">
-        <v>32</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
         <v>20</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT50AD+B</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>5.8</v>
+        <v>4.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2021/YG1_TOOLING</t>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>ER32</t>
-        </is>
+          <t>DER_DSK_COLLET:20</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>304.44</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>24956.13</v>
       </c>
     </row>
   </sheetData>
